--- a/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,8 +454,11 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,12 +544,27 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -603,8 +621,11 @@
         <v>0.1605195428467041</v>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,11 +682,26 @@
       <c r="P3" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -723,11 +759,26 @@
       <c r="P4" s="2" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1/6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>0.3333333333333333</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -785,11 +836,26 @@
       <c r="P5" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>0.3333333333333333</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -847,11 +913,26 @@
       <c r="P6" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -909,11 +990,26 @@
       <c r="P7" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -971,11 +1067,26 @@
       <c r="P8" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11.86510525800242</v>
+        <v>10.17834612260288</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2068941611579409</v>
+        <v>-0.3108792038122499</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1000468444108999</v>
+        <v>0.0830167089904766</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1719294100258575</v>
+        <v>0.164563240394407</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9001704061346208</v>
+        <v>0.9098267537631355</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.09572274373086342</v>
+        <v>0.09022589446255025</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.4097026426129917</v>
+        <v>0.3974800294591584</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5771359565859554</v>
+        <v>0.5599655894391498</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.2155995768964666</v>
+        <v>0.2455127207029907</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7822599407481463</v>
+        <v>0.6051970115039702</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20.70104422868237</v>
+        <v>11.86510525800242</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.3378223140484562</v>
+        <v>-0.2068941611579409</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1515647578588378</v>
+        <v>0.1000468444108999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2174146828851772</v>
+        <v>0.1719294100258575</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9078386821925589</v>
+        <v>0.9001704061346208</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1164167524321607</v>
+        <v>0.09572274373086342</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4100527879835336</v>
+        <v>0.4097026426129917</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5782988757141811</v>
+        <v>0.5771359565859554</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.2129016008977404</v>
+        <v>0.2155995768964666</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.084184136156412</v>
+        <v>0.7822599407481463</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0.6666666666666666</v>
@@ -919,31 +919,31 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2/6</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,47 +952,47 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17.68332688962617</v>
+        <v>20.70104422868237</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1517865845629425</v>
+        <v>0.3378223140484562</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1670801461517545</v>
+        <v>0.1515647578588378</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2202639677161539</v>
+        <v>0.2174146828851772</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9123828457824482</v>
+        <v>0.9078386821925589</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.110450887441977</v>
+        <v>0.1164167524321607</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3804224352313636</v>
+        <v>0.4100527879835336</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.534530836990221</v>
+        <v>0.5782988757141811</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.1958917707740646</v>
+        <v>0.2129016008977404</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.946115669774335</v>
+        <v>2.084184136156412</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
@@ -1015,12 +1015,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1029,61 +1029,138 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18.51854619740572</v>
+        <v>17.68332688962617</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2032760435630192</v>
+        <v>0.1517865845629425</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.5315036835710505</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1355466783927588</v>
+        <v>0.1670801461517545</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2121547953125522</v>
+        <v>0.2202639677161539</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9094007384265833</v>
+        <v>0.9123828457824482</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1121901247209223</v>
+        <v>0.110450887441977</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.402342892463353</v>
+        <v>0.3804224352313636</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.5668978085409568</v>
+        <v>0.534530836990221</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.211080615598264</v>
+        <v>0.1958917707740646</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.881544797159837</v>
+        <v>1.946115669774335</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>18.51854619740572</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.2032760435630192</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.1355466783927588</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.2121547953125522</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.9094007384265833</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.1121901247209223</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.402342892463353</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0.5668978085409568</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.211080615598264</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1.881544797159837</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1100,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1404,12 +1481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1418,60 +1495,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.4836144302039722</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.6365165293445558</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.3100613758801871</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.08703159251923893</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.1493056045470308</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9412742382271468</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.154578844788938</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.5965164192632566</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.3285703899194556</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.3100613758801871</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.7548820739334152</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.02505461866766034</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.060244241089977</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.1156623821440808</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1480,60 +1557,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1143103961605181</v>
+        <v>0.3232523550594082</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2291518234198189</v>
+        <v>0.4596274527008404</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2005953685030064</v>
+        <v>0.1029240628466189</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2047065010143791</v>
+        <v>0.1531765783358609</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9806094182825484</v>
+        <v>0.9484764542936288</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4742034398605797</v>
+        <v>-0.2531143766379184</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.007071403074654037</v>
+        <v>0.4104392274304347</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.007959461392532</v>
+        <v>0.538015984914983</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.119280498649606</v>
+        <v>0.7716934342675263</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.2379055525502543</v>
+        <v>0.03487440246540663</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.572047799034418</v>
+        <v>1.083856072122412</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1469831993585559</v>
+        <v>-0.1209745732692815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1542,110 +1619,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.06044405831575084</v>
+        <v>0.1143103961605181</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.169733991897312</v>
+        <v>0.2291518234198189</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2210688962956472</v>
+        <v>0.2005953685030064</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2075031531618561</v>
+        <v>0.2047065010143791</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9855955678670361</v>
+        <v>0.9806094182825484</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.4893559340541899</v>
+        <v>-0.4742034398605797</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03568578730644023</v>
+        <v>-0.007071403074654037</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.040167367540651</v>
+        <v>1.007959461392532</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.076679489756934</v>
+        <v>1.119280498649606</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2130216235535571</v>
+        <v>0.2379055525502543</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.512213984054911</v>
+        <v>1.572047799034418</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1510881223581858</v>
+        <v>-0.1469831993585559</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.06044405831575084</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.169733991897312</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.4938733180213994</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.2210688962956472</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2075031531618561</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9855955678670361</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.4893559340541899</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.03568578730644023</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.040167367540651</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.4938733180213994</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1.076679489756934</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.2130216235535571</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.512213984054911</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1510881223581858</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.1959791867971223</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.3192374434349921</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.4021145509405996</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1493682538447889</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1913411920973691</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9706371191135734</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3962590803105496</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.140120856124863</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.8422821421943985</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.4021145509405996</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.9809477008984322</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1571031582729965</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.377757118100216</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1449635134974329</v>
       </c>
     </row>
@@ -1660,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,12 +2103,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1978,60 +2117,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.4350331494949515</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.3622676312689921</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1166796953447241</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1997642353548091</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9244186046511628</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.2739414126958895</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.7298771057515232</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>1.268826669726443</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.06933303030489379</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.13114252804588</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1170212548420333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2040,60 +2179,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.07794149969959396</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0232828516603385</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2188856193116722</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2809242913791384</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9825581395348837</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5468101317287758</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.08721386877934878</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.085998179031943</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.378564869094712</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1210543375499389</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.228972710227808</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1959907093589865</v>
+        <v>-0.1240889646699911</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2102,110 +2241,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.01148643596579624</v>
+        <v>0.07794149969959396</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.03980250792897255</v>
+        <v>0.0232828516603385</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2469922875836444</v>
+        <v>0.2188856193116722</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2840766821769304</v>
+        <v>0.2809242913791384</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9941860465116279</v>
+        <v>0.9825581395348837</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5638362806438031</v>
+        <v>-0.5468101317287758</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1215068521088731</v>
+        <v>-0.08721386877934878</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.119813146320841</v>
+        <v>1.085998179031943</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.319052206952952</v>
+        <v>1.378564869094712</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.09300510126463379</v>
+        <v>0.1210543375499389</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.175917943401159</v>
+        <v>1.228972710227808</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1907361417385124</v>
+        <v>-0.1959907093589865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.01148643596579624</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-0.03980250792897255</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.5638362806438034</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.2469922875836444</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2840766821769304</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9941860465116279</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.5638362806438031</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1215068521088731</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.119813146320841</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.5638362806438034</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1.319052206952952</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.09300510126463379</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.175917943401159</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1907361417385124</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.09147296701545193</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.0361281855360438</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.2171366704425773</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2748323219326458</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9811046511627907</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.5315036835710507</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.05638459704404664</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.055598642040589</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>1.329736496831094</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.09804077200338912</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.18544284932526</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.197128506330739</v>
       </c>
     </row>
@@ -2220,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2524,12 +2725,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2538,60 +2739,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.004463254504794456</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>-0.01851322395813138</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1424709615053656</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.04623052871931452</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.1529248250153883</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9862068965517241</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1350492147242663</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.07505645280409468</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.691011962901241</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1424709615053656</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>0.1612952685910172</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>-0.08703698909779678</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>0.5929822223968276</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.02174145290462626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2600,60 +2801,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.07836937291241863</v>
+        <v>0.02427859728711668</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.05370233749755293</v>
+        <v>0.0008488550590588506</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04064383247477164</v>
+        <v>0.04278454166173134</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1705705942703356</v>
+        <v>0.1644125150610335</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8482758620689655</v>
+        <v>0.9241379310344827</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.07145768887935322</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>0.7058271448015913</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2662,110 +2863,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.08718588803191984</v>
+        <v>0.07836937291241863</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.06231718026233857</v>
+        <v>0.05370233749755293</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04200401516810738</v>
+        <v>0.04064383247477164</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1767962239874382</v>
+        <v>0.1705705942703356</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8206896551724138</v>
+        <v>0.8482758620689655</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.1377043507659563</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.0717563562167709</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.7045976084874375</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02856338737954378</v>
+        <v>-0.02590709634784172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.08718588803191984</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.06231718026233857</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.1492975281333249</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.04200401516810738</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.1767962239874382</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.8206896551724138</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.140631790481074</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.06811781052202481</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.7195765616634978</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.1492975281333249</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.2650990297168732</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.005430702683303479</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.9746039866510305</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.02856338737954378</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.05165909023225956</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.02760303608722836</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.04350725044042764</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1729842864844607</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.8758620689655172</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.0531550796975635</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.7811742611864783</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.2411450120325238</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.02426237512681706</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.8865399859777371</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.02438206875344118</v>
       </c>
     </row>
@@ -2780,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3084,12 +3347,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3098,19 +3361,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.005869330943017559</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>-0.08376291105473144</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.1140968231800305</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.4114240812492495</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3119,39 +3382,39 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.007998698566999085</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.980437851023039</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.4059102655834499</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.09103346041238103</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.7424559969061268</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.08544765322886072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3160,19 +3423,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.002382745880526116</v>
+        <v>0.007037250069187984</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08693880920546071</v>
+        <v>-0.08269906430310359</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.1167974844615735</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4880113830458718</v>
+        <v>0.4296396949184721</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3181,39 +3444,39 @@
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.474870734024246</v>
+        <v>0.418854880877529</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04644828317778826</v>
+        <v>-0.08266434720637639</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.868592529249625</v>
+        <v>0.7661331690981564</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.09631182261186377</v>
+        <v>-0.07820336667939509</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3222,110 +3485,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.008436531833865168</v>
+        <v>0.002382745880526116</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.09679398940886819</v>
+        <v>-0.08693880920546071</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1369242220207967</v>
+        <v>0.1335580210897492</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4907777251471288</v>
+        <v>0.4880113830458718</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4612806993661687</v>
+        <v>0.474870734024246</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.05523468091484574</v>
+        <v>-0.04644828317778826</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8437348117057034</v>
+        <v>0.868592529249625</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09747854570857184</v>
+        <v>-0.09631182261186377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.008436531833865168</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-0.09679398940886819</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1369242220207967</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.4907777251471288</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.321442164673614</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.04398902844387387</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.107582492397094</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.4612806993661687</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.05523468091484574</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.8437348117057034</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.09747854570857184</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.01467512388623127</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>-0.07574179554405092</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1265862887534693</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.4823761383388722</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9754098360655737</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.02350067883024798</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.057474822495967</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.4639662821985409</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.05349836459816792</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.8486470478528155</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.09627677960540704</v>
       </c>
     </row>
@@ -3340,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3644,12 +3969,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3658,60 +3983,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>-0.008347989224310126</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.06537597639031245</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1202141404246801</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.1643665908468291</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2214796402899178</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>0.128014615636332</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>0.7148394203240476</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.2737650318419123</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.1714433388946379</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.5094914103593154</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.09083171626673225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3720,60 +4045,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1581520768513234</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.09154899325217558</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1771492010844213</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2461249587924721</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9395711500974658</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3398215970939726</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04345354862296746</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.096795503018999</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3398215970939727</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7543016732344996</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1411353747440025</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.403795878337594</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1049631221034131</v>
+        <v>-0.07741687217408433</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3782,110 +4107,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1397885555120524</v>
+        <v>0.1581520768513234</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.07424152247084126</v>
+        <v>0.09154899325217558</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1818140869661326</v>
+        <v>0.1771492010844213</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2520711548688638</v>
+        <v>0.2461249587924721</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9395711500974658</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.343396896459686</v>
+        <v>-0.3398215970939726</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04863387549496068</v>
+        <v>-0.04345354862296746</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.108335005804564</v>
+        <v>1.096795503018999</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3433968964596861</v>
+        <v>-0.3398215970939727</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7358866404475835</v>
+        <v>0.7543016732344996</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1291567933740858</v>
+        <v>0.1411353747440025</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.369524514448298</v>
+        <v>1.403795878337594</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1077622875732581</v>
+        <v>-0.1049631221034131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.1397885555120524</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.07424152247084126</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1818140869661326</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2520711548688638</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9434697855750487</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.343396896459686</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.04863387549496068</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.108335005804564</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3433968964596861</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.7358866404475835</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1291567933740858</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.369524514448298</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1077622875732581</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.1273573073874552</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.06252517135729563</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.3457775114458427</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1821400660530844</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2502692357919135</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9454191033138402</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3407563776045505</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.04480797187624819</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.099812565704477</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.3408596999336523</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.7100769261764752</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1123681313006502</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.32149125162987</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1054534314823259</v>
       </c>
     </row>
@@ -3900,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4204,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4218,19 +4605,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.0520480753590512</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.04977130173806421</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.0653683722520295</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2161775406597309</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4239,39 +4626,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1284458931702925</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.5555413873337464</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.04770979298828082</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4280,19 +4667,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.03832826771717424</v>
+        <v>-0.04586689094251117</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.0360185421127458</v>
+        <v>-0.04357527146567408</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.09969672440806285</v>
+        <v>0.07490796810752959</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2832775140836015</v>
+        <v>0.233580415802233</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4301,39 +4688,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.03914997669357678</v>
+        <v>0.0903287250712983</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.8645301620965504</v>
+        <v>0.6874374194597751</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1928876156683936</v>
+        <v>0.1279826618159459</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.07233654476469098</v>
+        <v>-0.1228106656808624</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.6746549474635332</v>
+        <v>0.4476396044633588</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.06809052344706434</v>
+        <v>-0.04910852885624428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4342,19 +4729,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.02943793469695388</v>
+        <v>-0.03832826771717424</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.0271068564530339</v>
+        <v>-0.0360185421127458</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1050257154567922</v>
+        <v>0.09969672440806285</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2954859375373192</v>
+        <v>0.2832775140836015</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4363,39 +4750,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02452750015344596</v>
+        <v>0.03914997669357678</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9151280089903778</v>
+        <v>0.8645301620965504</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2210982371589283</v>
+        <v>0.1928876156683936</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.05039821439516878</v>
+        <v>-0.07233654476469098</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.7733260585852043</v>
+        <v>0.6746549474635332</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.07019594153968067</v>
+        <v>-0.06809052344706434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4404,19 +4791,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.04333413134981978</v>
+        <v>-0.02943793469695388</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.04103642873724656</v>
+        <v>-0.0271068564530339</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09995226162961648</v>
+        <v>0.1050257154567922</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2763396704990286</v>
+        <v>0.2954859375373192</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4425,27 +4812,89 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.02452750015344596</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.9151280089903778</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.2210982371589283</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.05039821439516878</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.7733260585852043</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.07019594153968067</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.04333413134981978</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-0.04103642873724656</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="G9" s="2" t="n">
+        <v>0.09995226162961648</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.2763396704990286</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>0.04972520692256377</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.827936916176494</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.1747232527765494</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.08646228085337915</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.61112221494444</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.07027295871809192</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10.17834612260288</v>
+        <v>11.86510525800242</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.3108792038122499</v>
+        <v>-0.2068941611579409</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0830167089904766</v>
+        <v>0.1000468444108999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.164563240394407</v>
+        <v>0.1719294100258575</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9098267537631355</v>
+        <v>0.9001704061346208</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.09022589446255025</v>
+        <v>0.09572274373086342</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3974800294591584</v>
+        <v>0.4097026426129917</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5599655894391498</v>
+        <v>0.5771359565859554</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.2455127207029907</v>
+        <v>0.2155995768964666</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.6051970115039702</v>
+        <v>0.7822599407481463</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11.86510525800242</v>
+        <v>20.70104422868237</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.2068941611579409</v>
+        <v>0.3378223140484562</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1000468444108999</v>
+        <v>0.1515647578588378</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1719294100258575</v>
+        <v>0.2174146828851772</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9001704061346208</v>
+        <v>0.9078386821925589</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.09572274373086342</v>
+        <v>0.1164167524321607</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4097026426129917</v>
+        <v>0.4100527879835336</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5771359565859554</v>
+        <v>0.5782988757141811</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.2155995768964666</v>
+        <v>0.2129016008977404</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7822599407481463</v>
+        <v>2.084184136156412</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0.6666666666666666</v>
@@ -919,31 +919,31 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,47 +952,47 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20.70104422868237</v>
+        <v>17.68332688962617</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.3378223140484562</v>
+        <v>0.1517865845629425</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1515647578588378</v>
+        <v>0.1670801461517545</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2174146828851772</v>
+        <v>0.2202639677161539</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9078386821925589</v>
+        <v>0.9123828457824482</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1164167524321607</v>
+        <v>0.110450887441977</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4100527879835336</v>
+        <v>0.3804224352313636</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.5782988757141811</v>
+        <v>0.534530836990221</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2129016008977404</v>
+        <v>0.1958917707740646</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>2.084184136156412</v>
+        <v>1.946115669774335</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
@@ -1015,12 +1015,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1029,138 +1029,61 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17.68332688962617</v>
+        <v>18.51854619740572</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1517865845629425</v>
+        <v>0.2032760435630192</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5315036835710505</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1670801461517545</v>
+        <v>0.1355466783927588</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2202639677161539</v>
+        <v>0.2121547953125522</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9123828457824482</v>
+        <v>0.9094007384265833</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.110450887441977</v>
+        <v>0.1121901247209223</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3804224352313636</v>
+        <v>0.402342892463353</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.534530836990221</v>
+        <v>0.5668978085409568</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1958917707740646</v>
+        <v>0.211080615598264</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.946115669774335</v>
+        <v>1.881544797159837</v>
       </c>
       <c r="P8" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2/6</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="U8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>18.51854619740572</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.2032760435630192</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1355466783927588</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2121547953125522</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9094007384265833</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.1121901247209223</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.402342892463353</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.5668978085409568</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.211080615598264</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1.881544797159837</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1177,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1481,12 +1404,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1495,60 +1418,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4836144302039722</v>
+        <v>0.3232523550594082</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6365165293445558</v>
+        <v>0.4596274527008404</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.08703159251923893</v>
+        <v>0.1029240628466189</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1493056045470308</v>
+        <v>0.1531765783358609</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9412742382271468</v>
+        <v>0.9484764542936288</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.154578844788938</v>
+        <v>-0.2531143766379184</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.5965164192632566</v>
+        <v>0.4104392274304347</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.3285703899194556</v>
+        <v>0.538015984914983</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7548820739334152</v>
+        <v>0.7716934342675263</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.02505461866766034</v>
+        <v>0.03487440246540663</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.060244241089977</v>
+        <v>1.083856072122412</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.1209745732692815</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1557,60 +1480,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.1143103961605181</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.2291518234198189</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.2005953685030064</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2047065010143791</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9806094182825484</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.4742034398605797</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>-0.007071403074654037</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>1.007959461392532</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>1.119280498649606</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.2379055525502543</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.572047799034418</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.1469831993585559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1619,60 +1542,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1143103961605181</v>
+        <v>0.06044405831575084</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2291518234198189</v>
+        <v>0.169733991897312</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2005953685030064</v>
+        <v>0.2210688962956472</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2047065010143791</v>
+        <v>0.2075031531618561</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9806094182825484</v>
+        <v>0.9855955678670361</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.4742034398605797</v>
+        <v>-0.4893559340541899</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.007071403074654037</v>
+        <v>-0.03568578730644023</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.007959461392532</v>
+        <v>1.040167367540651</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.119280498649606</v>
+        <v>1.076679489756934</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2379055525502543</v>
+        <v>0.2130216235535571</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.572047799034418</v>
+        <v>1.512213984054911</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1469831993585559</v>
+        <v>-0.1510881223581858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1681,110 +1604,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.06044405831575084</v>
+        <v>0.1959791867971223</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.169733991897312</v>
+        <v>0.3192374434349921</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4021145509405996</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2210688962956472</v>
+        <v>0.1493682538447889</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2075031531618561</v>
+        <v>0.1913411920973691</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9855955678670361</v>
+        <v>0.9706371191135734</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.4893559340541899</v>
+        <v>-0.3962590803105496</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.03568578730644023</v>
+        <v>0.140120856124863</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.040167367540651</v>
+        <v>0.8422821421943985</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4021145509405996</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.076679489756934</v>
+        <v>0.9809477008984322</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.2130216235535571</v>
+        <v>0.1571031582729965</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.512213984054911</v>
+        <v>1.377757118100216</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1510881223581858</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.1959791867971223</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.3192374434349921</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.4021145509405996</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1493682538447889</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1913411920973691</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9706371191135734</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3962590803105496</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.140120856124863</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.8422821421943985</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.4021145509405996</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9809477008984322</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1571031582729965</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.377757118100216</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1449635134974329</v>
       </c>
     </row>
@@ -1799,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2103,12 +1964,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2117,60 +1978,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4350331494949515</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.3622676312689921</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1166796953447241</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1997642353548091</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.268826669726443</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.06933303030489379</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.13114252804588</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1170212548420333</v>
+        <v>-0.1240889646699911</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2179,60 +2040,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.07794149969959396</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.0232828516603385</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.2188856193116722</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.2809242913791384</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9825581395348837</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.5468101317287758</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>-0.08721386877934878</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>1.085998179031943</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>1.378564869094712</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.1210543375499389</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.228972710227808</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1959907093589865</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2241,60 +2102,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.07794149969959396</v>
+        <v>0.01148643596579624</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.0232828516603385</v>
+        <v>-0.03980250792897255</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2188856193116722</v>
+        <v>0.2469922875836444</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2809242913791384</v>
+        <v>0.2840766821769304</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9825581395348837</v>
+        <v>0.9941860465116279</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5468101317287758</v>
+        <v>-0.5638362806438031</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.08721386877934878</v>
+        <v>-0.1215068521088731</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.085998179031943</v>
+        <v>1.119813146320841</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.378564869094712</v>
+        <v>1.319052206952952</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1210543375499389</v>
+        <v>0.09300510126463379</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.228972710227808</v>
+        <v>1.175917943401159</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1959907093589865</v>
+        <v>-0.1907361417385124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2303,110 +2164,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.01148643596579624</v>
+        <v>0.09147296701545193</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.03980250792897255</v>
+        <v>0.0361281855360438</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2469922875836444</v>
+        <v>0.2171366704425773</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2840766821769304</v>
+        <v>0.2748323219326458</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9941860465116279</v>
+        <v>0.9811046511627907</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5638362806438031</v>
+        <v>-0.5315036835710507</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1215068521088731</v>
+        <v>-0.05638459704404664</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.119813146320841</v>
+        <v>1.055598642040589</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.319052206952952</v>
+        <v>1.329736496831094</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.09300510126463379</v>
+        <v>0.09804077200338912</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.175917943401159</v>
+        <v>1.18544284932526</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1907361417385124</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.09147296701545193</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.0361281855360438</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.2171366704425773</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2748323219326458</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9811046511627907</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.5315036835710507</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.05638459704404664</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.055598642040589</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1.329736496831094</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.09804077200338912</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.18544284932526</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.197128506330739</v>
       </c>
     </row>
@@ -2421,7 +2220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2725,12 +2524,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2739,60 +2538,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.004463254504794456</v>
+        <v>0.02427859728711668</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.01851322395813138</v>
+        <v>0.0008488550590588506</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04623052871931452</v>
+        <v>0.04278454166173134</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1529248250153883</v>
+        <v>0.1644125150610335</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9241379310344827</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1350492147242663</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07505645280409468</v>
+        <v>0.07145768887935322</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.691011962901241</v>
+        <v>0.7058271448015913</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1612952685910172</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08703698909779678</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5929822223968276</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02174145290462626</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2801,60 +2600,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.07836937291241863</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.05370233749755293</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.04064383247477164</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.1705705942703356</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.8482758620689655</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1377043507659563</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.0717563562167709</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.7045976084874375</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.02590709634784172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2863,60 +2662,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.07836937291241863</v>
+        <v>0.08718588803191984</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.05370233749755293</v>
+        <v>0.06231718026233857</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04064383247477164</v>
+        <v>0.04200401516810738</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1705705942703356</v>
+        <v>0.1767962239874382</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8482758620689655</v>
+        <v>0.8206896551724138</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.140631790481074</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>0.06811781052202481</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>0.7195765616634978</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>0.2650990297168732</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>-0.005430702683303479</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>0.9746039866510305</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.02856338737954378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2925,110 +2724,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.08718588803191984</v>
+        <v>0.05165909023225956</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.06231718026233857</v>
+        <v>0.02760303608722836</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.04200401516810738</v>
+        <v>0.04350725044042764</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1767962239874382</v>
+        <v>0.1729842864844607</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8206896551724138</v>
+        <v>0.8758620689655172</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.0531550796975635</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.7811742611864783</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>0.2411450120325238</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>-0.02426237512681706</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>0.8865399859777371</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02856338737954378</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.05165909023225956</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.02760303608722836</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.04350725044042764</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1729842864844607</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.8758620689655172</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.0531550796975635</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.7811742611864783</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.2411450120325238</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.02426237512681706</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.8865399859777371</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.02438206875344118</v>
       </c>
     </row>
@@ -3043,7 +2780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3347,12 +3084,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3361,19 +3098,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.005869330943017559</v>
+        <v>0.007037250069187984</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08376291105473144</v>
+        <v>-0.08269906430310359</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.1167974844615735</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4114240812492495</v>
+        <v>0.4296396949184721</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3382,39 +3119,39 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.007998698566999085</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.980437851023039</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4059102655834499</v>
+        <v>0.418854880877529</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09103346041238103</v>
+        <v>-0.08266434720637639</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7424559969061268</v>
+        <v>0.7661331690981564</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.08544765322886072</v>
+        <v>-0.07820336667939509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3423,19 +3160,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.002382745880526116</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>-0.08693880920546071</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.1335580210897492</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.4880113830458718</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3444,39 +3181,39 @@
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.474870734024246</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.04644828317778826</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.868592529249625</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.09631182261186377</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3485,60 +3222,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.002382745880526116</v>
+        <v>-0.008436531833865168</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.08693880920546071</v>
+        <v>-0.09679398940886819</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.1369242220207967</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4880113830458718</v>
+        <v>0.4907777251471288</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.474870734024246</v>
+        <v>0.4612806993661687</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.04644828317778826</v>
+        <v>-0.05523468091484574</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.868592529249625</v>
+        <v>0.8437348117057034</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09631182261186377</v>
+        <v>-0.09747854570857184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3547,110 +3284,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.008436531833865168</v>
+        <v>0.01467512388623127</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.09679398940886819</v>
+        <v>-0.07574179554405092</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1369242220207967</v>
+        <v>0.1265862887534693</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4907777251471288</v>
+        <v>0.4823761383388722</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>0.9754098360655737</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4612806993661687</v>
+        <v>0.4639662821985409</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.05523468091484574</v>
+        <v>-0.05349836459816792</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8437348117057034</v>
+        <v>0.8486470478528155</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.09747854570857184</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.01467512388623127</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.07574179554405092</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1265862887534693</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.4823761383388722</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9754098360655737</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.02350067883024798</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.057474822495967</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.4639662821985409</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.05349836459816792</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.8486470478528155</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.09627677960540704</v>
       </c>
     </row>
@@ -3665,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3969,12 +3644,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3983,60 +3658,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.008347989224310126</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.06537597639031245</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1202141404246801</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1643665908468291</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2214796402899178</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.128014615636332</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7148394203240476</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2737650318419123</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1714433388946379</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5094914103593154</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.07741687217408433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4045,60 +3720,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.1581520768513234</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>0.09154899325217558</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1771492010844213</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.2461249587924721</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9395711500974658</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.3398215970939726</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-0.04345354862296746</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.096795503018999</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3398215970939727</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.7543016732344996</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>0.1411353747440025</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>1.403795878337594</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.1049631221034131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4107,60 +3782,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1581520768513234</v>
+        <v>0.1397885555120524</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09154899325217558</v>
+        <v>0.07424152247084126</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1771492010844213</v>
+        <v>0.1818140869661326</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2461249587924721</v>
+        <v>0.2520711548688638</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9395711500974658</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3398215970939726</v>
+        <v>-0.343396896459686</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04345354862296746</v>
+        <v>-0.04863387549496068</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.096795503018999</v>
+        <v>1.108335005804564</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3398215970939727</v>
+        <v>-0.3433968964596861</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7543016732344996</v>
+        <v>0.7358866404475835</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1411353747440025</v>
+        <v>0.1291567933740858</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.403795878337594</v>
+        <v>1.369524514448298</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1049631221034131</v>
+        <v>-0.1077622875732581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4169,110 +3844,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.1397885555120524</v>
+        <v>0.1273573073874552</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.07424152247084126</v>
+        <v>0.06252517135729563</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1818140869661326</v>
+        <v>0.1821400660530844</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2520711548688638</v>
+        <v>0.2502692357919135</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9454191033138402</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.343396896459686</v>
+        <v>-0.3407563776045505</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.04863387549496068</v>
+        <v>-0.04480797187624819</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.108335005804564</v>
+        <v>1.099812565704477</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3433968964596861</v>
+        <v>-0.3408596999336523</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.7358866404475835</v>
+        <v>0.7100769261764752</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1291567933740858</v>
+        <v>0.1123681313006502</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.369524514448298</v>
+        <v>1.32149125162987</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1077622875732581</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.1273573073874552</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.06252517135729563</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1821400660530844</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2502692357919135</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9454191033138402</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3407563776045505</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.04480797187624819</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.099812565704477</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.3408596999336523</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7100769261764752</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1123681313006502</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.32149125162987</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1054534314823259</v>
       </c>
     </row>
@@ -4287,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4591,12 +4204,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4605,19 +4218,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>-0.04586689094251117</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>-0.04357527146567408</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0.07490796810752959</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>0.233580415802233</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4626,39 +4239,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.0903287250712983</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>0.6874374194597751</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.1279826618159459</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.1228106656808624</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.4476396044633588</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.04910852885624428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4667,19 +4280,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.03832826771717424</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.0360185421127458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.09969672440806285</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2832775140836015</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4688,39 +4301,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.03914997669357678</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.8645301620965504</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.1928876156683936</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.07233654476469098</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.6746549474635332</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.06809052344706434</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4729,19 +4342,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.03832826771717424</v>
+        <v>-0.02943793469695388</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.0360185421127458</v>
+        <v>-0.0271068564530339</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.09969672440806285</v>
+        <v>0.1050257154567922</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2832775140836015</v>
+        <v>0.2954859375373192</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4750,39 +4363,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03914997669357678</v>
+        <v>0.02452750015344596</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8645301620965504</v>
+        <v>0.9151280089903778</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.1928876156683936</v>
+        <v>0.2210982371589283</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.07233654476469098</v>
+        <v>-0.05039821439516878</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.6746549474635332</v>
+        <v>0.7733260585852043</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.06809052344706434</v>
+        <v>-0.07019594153968067</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4791,19 +4404,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.02943793469695388</v>
+        <v>-0.04333413134981978</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.0271068564530339</v>
+        <v>-0.04103642873724656</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1050257154567922</v>
+        <v>0.09995226162961648</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2954859375373192</v>
+        <v>0.2763396704990286</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4812,89 +4425,27 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.02452750015344596</v>
+        <v>0.04972520692256377</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.9151280089903778</v>
+        <v>0.827936916176494</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2210982371589283</v>
+        <v>0.1747232527765494</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.05039821439516878</v>
+        <v>-0.08646228085337915</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.7733260585852043</v>
+        <v>0.61112221494444</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.07019594153968067</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.04333413134981978</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.04103642873724656</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.09995226162961648</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2763396704990286</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.04972520692256377</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.827936916176494</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.1747232527765494</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.08646228085337915</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.61112221494444</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.07027295871809192</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_quarterly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,27 +681,27 @@
         <v>0.5267967133353264</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -757,27 +758,27 @@
         <v>1.258981438936668</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -834,27 +835,27 @@
         <v>0.7822599407481463</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -911,27 +912,27 @@
         <v>2.084184136156412</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -988,27 +989,27 @@
         <v>1.946115669774335</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1066,27 @@
         <v>1.881544797159837</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1232,28 +1233,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1262,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1274,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
     </row>
     <row r="3">
@@ -1294,49 +1295,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1329371506140695</v>
+        <v>0.07457653000238507</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2496982611806651</v>
+        <v>0.01716750826567259</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.3856720855668119</v>
+        <v>-0.1710347256874637</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1522759239856132</v>
+        <v>0.08553463970067471</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1730383638967156</v>
+        <v>0.2968486464003908</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9789473684210527</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3649758682045836</v>
+        <v>-0.1695376301830119</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.1991969289988629</v>
+        <v>0.0002300732610018841</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.7757870327657773</v>
+        <v>0.9988745374904231</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3856720855668119</v>
+        <v>-0.1710347256874637</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.7840851928113244</v>
+        <v>0.2939496948419145</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.04211262634233282</v>
+        <v>0.01693353905012085</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.101260500028059</v>
+        <v>1.079097002930638</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1434104009961642</v>
+        <v>-0.07409475278464162</v>
       </c>
     </row>
     <row r="4">
@@ -1356,49 +1357,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.1406064183528005</v>
+        <v>0.03065849396422626</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.05203685476090714</v>
+        <v>-0.02440421607187349</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3325799988927458</v>
+        <v>0.0958017749538176</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1798617631710739</v>
+        <v>0.3109311052344195</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.5086297155507329</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.07208292313732823</v>
+        <v>0.0009345351247636025</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.081135417924184</v>
+        <v>0.9954284811619402</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.7489734500538974</v>
+        <v>0.2401923912366097</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.02160329718706966</v>
+        <v>-0.02531509335271243</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.051945482042245</v>
+        <v>0.8817525381326254</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1427514496479956</v>
+        <v>-0.1050869895001562</v>
       </c>
     </row>
     <row r="5">
@@ -1418,49 +1419,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
     </row>
     <row r="6">
@@ -1480,49 +1481,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1143103961605181</v>
+        <v>0.09041417313448719</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2291518234198189</v>
+        <v>0.03215902869413889</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2005953685030064</v>
+        <v>0.08759061925316305</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2047065010143791</v>
+        <v>0.3130992931150791</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9806094182825484</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4742034398605797</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.007071403074654037</v>
+        <v>-0.008548633056465471</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.007959461392532</v>
+        <v>1.041817836506867</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.119280498649606</v>
+        <v>0.324646577182107</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.2379055525502543</v>
+        <v>0.04105865714432233</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.572047799034418</v>
+        <v>1.191786059302786</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1469831993585559</v>
+        <v>-0.08202293348751755</v>
       </c>
     </row>
     <row r="7">
@@ -1542,49 +1543,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.06044405831575084</v>
+        <v>0.09065154909918771</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.169733991897312</v>
+        <v>0.03238372289859548</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2210688962956472</v>
+        <v>0.08644743295588117</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2075031531618561</v>
+        <v>0.3107776446448876</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9855955678670361</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.4893559340541899</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03568578730644023</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.040167367540651</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.076679489756934</v>
+        <v>0.3231448312415395</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2130216235535571</v>
+        <v>0.03987841356902466</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.512213984054911</v>
+        <v>1.186273110753881</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1510881223581858</v>
+        <v>-0.07734267826577679</v>
       </c>
     </row>
     <row r="8">
@@ -1604,49 +1605,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.1959791867971223</v>
+        <v>0.09697834317649545</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.3192374434349921</v>
+        <v>0.03837250935283798</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1493682538447889</v>
+        <v>0.07784184823645553</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1913411920973691</v>
+        <v>0.2927487227303591</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3962590803105496</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.140120856124863</v>
+        <v>0.006450126263573663</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8422821421943985</v>
+        <v>0.9684475490108004</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9809477008984322</v>
+        <v>0.3127612378554672</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1571031582729965</v>
+        <v>0.03171779927911134</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.377757118100216</v>
+        <v>1.14815466838371</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1449635134974329</v>
+        <v>-0.06187989028444074</v>
       </c>
     </row>
   </sheetData>
@@ -1792,28 +1793,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1822,10 +1823,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1834,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
     </row>
     <row r="3">
@@ -1854,49 +1855,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.06596889581842613</v>
+        <v>0.1368982599870656</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.01191733669989281</v>
+        <v>0.2510346643381476</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.5346210465276369</v>
+        <v>-0.3856720855668119</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.2281604573233378</v>
+        <v>0.1523602176604615</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.252378609295607</v>
+        <v>0.1731316244691005</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9854651162790697</v>
+        <v>0.9789240155296728</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.5346210465276369</v>
+        <v>-0.3636703927702163</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.06266339070641924</v>
+        <v>0.2023422558043573</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.061789914472815</v>
+        <v>0.7725203341546685</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.5346210465276369</v>
+        <v>-0.3856720855668119</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.290539543881048</v>
+        <v>0.7866499485014886</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.07956664304674876</v>
+        <v>0.04049795996000793</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.150499273887041</v>
+        <v>1.096971768738965</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1579621820209069</v>
+        <v>-0.1434104009961642</v>
       </c>
     </row>
     <row r="4">
@@ -1916,49 +1917,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2807829634843186</v>
+        <v>-0.1441435513209015</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2158389333720412</v>
+        <v>-0.05822172248985902</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1673128535837262</v>
+        <v>0.3327436642745257</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2148728007780382</v>
+        <v>0.179942036489818</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9476744186046512</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.4418768397766435</v>
+        <v>-0.5118569259989467</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.1241360759195709</v>
+        <v>-0.07765560790925141</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.8775942790903688</v>
+        <v>1.087302929721673</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.294803467700139</v>
+        <v>0.7532901607393325</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.08157629615921302</v>
+        <v>0.0210700965778523</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.154300506697793</v>
+        <v>1.050452035971018</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1198660820476312</v>
+        <v>-0.1427514496479956</v>
       </c>
     </row>
     <row r="5">
@@ -1978,49 +1979,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.3294578948487177</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.4629259009092757</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1029808820995737</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1532558675077065</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.2514292974161799</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.414421357968767</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.5340941927569753</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>0.7759950933958086</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.03429285245675695</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.082113730200731</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1209745732692815</v>
       </c>
     </row>
     <row r="6">
@@ -2040,49 +2041,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.07794149969959396</v>
+        <v>0.1137402955357241</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0232828516603385</v>
+        <v>0.2255518068971762</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2188856193116722</v>
+        <v>0.2007065323816303</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2809242913791384</v>
+        <v>0.2048198630871046</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9825581395348837</v>
+        <v>0.9811425402107599</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5468101317287758</v>
+        <v>-0.4746076449481669</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.08721386877934878</v>
+        <v>-0.007273239877282123</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.085998179031943</v>
+        <v>1.008176809981286</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.378564869094712</v>
+        <v>1.119825849818175</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1210543375499389</v>
+        <v>0.2345308458751303</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.228972710227808</v>
+        <v>1.561580656675442</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1959907093589865</v>
+        <v>-0.1469831993585559</v>
       </c>
     </row>
     <row r="7">
@@ -2102,49 +2103,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.01148643596579624</v>
+        <v>0.05839323605780855</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.03980250792897255</v>
+        <v>0.1646483009169268</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2469922875836444</v>
+        <v>0.2211914060841004</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2840766821769304</v>
+        <v>0.2076175838581398</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9941860465116279</v>
+        <v>0.9866888519134775</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5638362806438031</v>
+        <v>-0.4900454549092432</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1215068521088731</v>
+        <v>-0.03644292024794071</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.119813146320841</v>
+        <v>1.040970301964238</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.319052206952952</v>
+        <v>1.075465835625498</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.09300510126463379</v>
+        <v>0.2086967398097597</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.175917943401159</v>
+        <v>1.499721270142814</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1907361417385124</v>
+        <v>-0.1510881223581858</v>
       </c>
     </row>
     <row r="8">
@@ -2164,49 +2165,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.09147296701545193</v>
+        <v>0.1992071128489044</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0361281855360438</v>
+        <v>0.3195988776620315</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2171366704425773</v>
+        <v>0.1494510221753559</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2748323219326458</v>
+        <v>0.1914457407943713</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9811046511627907</v>
+        <v>0.9706045479755963</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5315036835710507</v>
+        <v>-0.3956369736729515</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.05638459704404664</v>
+        <v>0.1419415286399084</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.055598642040589</v>
+        <v>0.8404247724914087</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.329736496831094</v>
+        <v>0.9842496324385637</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.09804077200338912</v>
+        <v>0.1555748210976431</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.18544284932526</v>
+        <v>1.372521618076181</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.197128506330739</v>
+        <v>-0.1449635134974329</v>
       </c>
     </row>
   </sheetData>
@@ -2352,28 +2353,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2382,10 +2383,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2394,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
     </row>
     <row r="3">
@@ -2414,49 +2415,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0278113162498399</v>
+        <v>0.06596889581842613</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.004300765250730976</v>
+        <v>0.01191733669989281</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.1648378301232092</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05426713453700898</v>
+        <v>0.2281604573233378</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1808388629734859</v>
+        <v>0.252378609295607</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9172413793103448</v>
+        <v>0.9854651162790697</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1647110860703804</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03818940009343752</v>
+        <v>-0.06266339070641924</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.8427841000739825</v>
+        <v>1.061789914472815</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.1648378301232092</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2304860020402977</v>
+        <v>1.290539543881048</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.03264205436855394</v>
+        <v>0.07956664304674876</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8473534463541423</v>
+        <v>1.150499273887041</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02614394426954258</v>
+        <v>-0.1579621820209069</v>
       </c>
     </row>
     <row r="4">
@@ -2476,49 +2477,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.005584530641855379</v>
+        <v>0.2807829634843186</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.01741759632229589</v>
+        <v>0.2158389333720412</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.07919440518124658</v>
+        <v>0.1673128535837262</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2118816077559385</v>
+        <v>0.2148728007780382</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9476744186046512</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766435</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.003021666415692792</v>
+        <v>0.1241360759195709</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9875605795415207</v>
+        <v>0.8775942790903688</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2460863607380916</v>
+        <v>1.294803467700139</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.02037768816203989</v>
+        <v>0.08157629615921302</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9047062469143489</v>
+        <v>1.154300506697793</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.03283822635553391</v>
+        <v>-0.1198660820476312</v>
       </c>
     </row>
     <row r="5">
@@ -2538,49 +2539,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
     </row>
     <row r="6">
@@ -2600,49 +2601,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.07836937291241863</v>
+        <v>0.07794149969959396</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.05370233749755293</v>
+        <v>0.0232828516603385</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04064383247477164</v>
+        <v>0.2188856193116722</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1705705942703356</v>
+        <v>0.2809242913791384</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8482758620689655</v>
+        <v>0.9825581395348837</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1377043507659563</v>
+        <v>-0.5468101317287758</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0717563562167709</v>
+        <v>-0.08721386877934878</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7045976084874375</v>
+        <v>1.085998179031943</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2505796287738526</v>
+        <v>1.378564869094712</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.01684526395807662</v>
+        <v>0.1210543375499389</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9212251943636144</v>
+        <v>1.228972710227808</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02590709634784172</v>
+        <v>-0.1959907093589865</v>
       </c>
     </row>
     <row r="7">
@@ -2662,49 +2663,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.08718588803191984</v>
+        <v>0.01148643596579624</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.06231718026233857</v>
+        <v>-0.03980250792897255</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04200401516810738</v>
+        <v>0.2469922875836444</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1767962239874382</v>
+        <v>0.2840766821769304</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8206896551724138</v>
+        <v>0.9941860465116279</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.5638362806438031</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>-0.1215068521088731</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>1.119813146320841</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>1.319052206952952</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>0.09300510126463379</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>1.175917943401159</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02856338737954378</v>
+        <v>-0.1907361417385124</v>
       </c>
     </row>
     <row r="8">
@@ -2724,49 +2725,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.05165909023225956</v>
+        <v>0.09147296701545193</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.02760303608722836</v>
+        <v>0.0361281855360438</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.04350725044042764</v>
+        <v>0.2171366704425773</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1729842864844607</v>
+        <v>0.2748323219326458</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.9811046511627907</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710507</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.0531550796975635</v>
+        <v>-0.05638459704404664</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.7811742611864783</v>
+        <v>1.055598642040589</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2411450120325238</v>
+        <v>1.329736496831094</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.02426237512681706</v>
+        <v>0.09804077200338912</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8865399859777371</v>
+        <v>1.18544284932526</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02438206875344118</v>
+        <v>-0.197128506330739</v>
       </c>
     </row>
   </sheetData>
@@ -2912,28 +2913,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2942,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2954,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
     </row>
     <row r="3">
@@ -2974,49 +2975,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.01796626895340192</v>
+        <v>0.02638711980247832</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.07274392188106338</v>
+        <v>0.007336273573639973</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1658685120345931</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1239950883001488</v>
+        <v>0.05495589287611802</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4573896848585784</v>
+        <v>0.1802260928296245</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9246575342465754</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1658685120345931</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.01981061610580925</v>
+        <v>0.04132733712762127</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.048450159778007</v>
+        <v>0.8336239198261057</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1658685120345931</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.463185537603793</v>
+        <v>0.2304860020402977</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.05400314127557215</v>
+        <v>-0.03264205436855394</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8472189772776864</v>
+        <v>0.8473534463541423</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.07526187495033521</v>
+        <v>-0.02614394426954258</v>
       </c>
     </row>
     <row r="4">
@@ -3036,49 +3037,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03653107044182335</v>
+        <v>0.003018060423530589</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.05583341556643984</v>
+        <v>-0.01559903098887294</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1224269746777639</v>
+        <v>0.07892753856493077</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4598626791204086</v>
+        <v>0.2111772154448013</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.02087617766040506</v>
+        <v>0.004878060774464288</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.051056167955528</v>
+        <v>0.9803618455261432</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.4914912653967582</v>
+        <v>0.2460863607380916</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.03570257112374731</v>
+        <v>-0.02037768816203989</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8989933696214515</v>
+        <v>0.9047062469143489</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.06498956817109347</v>
+        <v>-0.03283822635553391</v>
       </c>
     </row>
     <row r="5">
@@ -3098,49 +3099,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.02497427700722055</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>0.005949654656603798</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.04263876767180749</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.1638459834801125</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="6">
@@ -3160,49 +3161,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.002382745880526116</v>
+        <v>0.07634464914699279</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08693880920546071</v>
+        <v>0.05636653757045784</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.0405134002783077</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4880113830458718</v>
+        <v>0.1700106362471846</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04246285263122429</v>
+        <v>0.07446620439756768</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.103849975367978</v>
+        <v>0.7002130779721872</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.474870734024246</v>
+        <v>0.2505796287738526</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04644828317778826</v>
+        <v>-0.01684526395807662</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.868592529249625</v>
+        <v>0.9212251943636144</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.09631182261186377</v>
+        <v>-0.02590709634784172</v>
       </c>
     </row>
     <row r="7">
@@ -3222,49 +3223,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.008436531833865168</v>
+        <v>0.08432370578342496</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.09679398940886819</v>
+        <v>0.06419749435440836</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1369242220207967</v>
+        <v>0.04186991637394554</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4907777251471288</v>
+        <v>0.176236075214825</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.8287671232876712</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4612806993661687</v>
+        <v>0.2650990297168732</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.05523468091484574</v>
+        <v>-0.005430702683303479</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8437348117057034</v>
+        <v>0.9746039866510305</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09747854570857184</v>
+        <v>-0.02856338737954378</v>
       </c>
     </row>
     <row r="8">
@@ -3284,49 +3285,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.01467512388623127</v>
+        <v>0.04973873152688491</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.07574179554405092</v>
+        <v>0.03025445432880103</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1265862887534693</v>
+        <v>0.04449667859819988</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4823761383388722</v>
+        <v>0.1724104395842316</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9754098360655737</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.02350067883024798</v>
+        <v>0.05587242724467401</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.057474822495967</v>
+        <v>0.77506812485731</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4639662821985409</v>
+        <v>0.2411450120325238</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.05349836459816792</v>
+        <v>-0.02426237512681706</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8486470478528155</v>
+        <v>0.8865399859777371</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.09627677960540704</v>
+        <v>-0.02438206875344118</v>
       </c>
     </row>
   </sheetData>
@@ -3472,28 +3473,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -3502,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -3514,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
     </row>
     <row r="3">
@@ -3534,49 +3535,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1000852633438949</v>
+        <v>0.01764348451762343</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.03682148976427913</v>
+        <v>-0.08432417426045935</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.2929230698083376</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1470733778286762</v>
+        <v>0.1220275198399813</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2061258002604127</v>
+        <v>0.4500432450769836</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9682539682539683</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.2929230698083375</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.02449871951002813</v>
+        <v>-0.01981061610580925</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.9454275668284279</v>
+        <v>1.048450159778007</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.2929230698083376</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.5558211792395804</v>
+        <v>0.4627215796784678</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.01202809727292231</v>
+        <v>-0.06581744223585062</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.034413031544071</v>
+        <v>0.8178514942398586</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.08781007621197889</v>
+        <v>-0.07526187495033521</v>
       </c>
     </row>
     <row r="4">
@@ -3596,49 +3597,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03277746210192878</v>
+        <v>0.04820889971753206</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.02661557014535587</v>
+        <v>-0.05682140710471517</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1728680437397538</v>
+        <v>0.120483568435348</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2051485421432778</v>
+        <v>0.4525656398613154</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.98635477582846</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2963782229283601</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.01949247507462459</v>
+        <v>-0.02087617766040506</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9565792900758322</v>
+        <v>1.051056167955528</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.2963782229283602</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.4678020148838795</v>
+        <v>0.5082947948424215</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.0452264693926312</v>
+        <v>-0.0367116279107782</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8706046448976331</v>
+        <v>0.8984012756981892</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.09352882951066699</v>
+        <v>-0.06498956817109347</v>
       </c>
     </row>
     <row r="5">
@@ -3658,49 +3659,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.009125074064342265</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.09198904181424106</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1149439295311541</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.4227552867946717</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.4217964992394458</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.09195467631537591</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.7455172015271687</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.07820336667939509</v>
       </c>
     </row>
     <row r="6">
@@ -3720,49 +3721,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1581520768513234</v>
+        <v>-0.007252311911813636</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.09154899325217558</v>
+        <v>-0.1067254172299203</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1771492010844213</v>
+        <v>0.1314438165933432</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2461249587924721</v>
+        <v>0.4802226182450062</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9395711500974658</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3398215970939726</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04345354862296746</v>
+        <v>-0.04246285263122429</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.096795503018999</v>
+        <v>1.103849975367978</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3398215970939727</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7543016732344996</v>
+        <v>0.4606940487042375</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1411353747440025</v>
+        <v>-0.06711234626801021</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.403795878337594</v>
+        <v>0.8142678722310382</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1049631221034131</v>
+        <v>-0.09631182261186377</v>
       </c>
     </row>
     <row r="7">
@@ -3782,49 +3783,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1397885555120524</v>
+        <v>-0.01801583075704949</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.07424152247084126</v>
+        <v>-0.1164104337965486</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1818140869661326</v>
+        <v>0.1347774917962256</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2520711548688638</v>
+        <v>0.4829467702160691</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.343396896459686</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04863387549496068</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.108335005804564</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3433968964596861</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7358866404475835</v>
+        <v>0.4471635549983983</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1291567933740858</v>
+        <v>-0.07575373871995661</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.369524514448298</v>
+        <v>0.7903529847887605</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1077622875732581</v>
+        <v>-0.09747854570857184</v>
       </c>
     </row>
     <row r="8">
@@ -3844,49 +3845,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.1273573073874552</v>
+        <v>0.003147169989504262</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.06252517135729563</v>
+        <v>-0.09736796118354629</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1821400660530844</v>
+        <v>0.1245853659936119</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2502692357919135</v>
+        <v>0.4747180043938371</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9454191033138402</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3407563776045505</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.04480797187624819</v>
+        <v>-0.02350067883024798</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.099812565704477</v>
+        <v>1.057474822495967</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3408596999336523</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.7100769261764752</v>
+        <v>0.4473338296920579</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1123681313006502</v>
+        <v>-0.07564499099171129</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.32149125162987</v>
+        <v>0.7906539420355296</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1054534314823259</v>
+        <v>-0.09627677960540704</v>
       </c>
     </row>
   </sheetData>
@@ -4032,25 +4033,585 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.179974191375289</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.240579627043532</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.9746588693957114</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-0.3098313187450096</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-0.3098313187450098</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.5373300241683001</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>-0.1055402030174765</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.1000852633438949</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.03682148976427913</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1470733778286762</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.2061258002604127</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.2929230698083375</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.02449871951002813</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.9454275668284279</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.5558211792395804</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.01202809727292231</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1.034413031544071</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-0.08781007621197889</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.03277746210192878</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-0.02661557014535587</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1728680437397538</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.2051485421432778</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.98635477582846</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.2963782229283601</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.01949247507462459</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.9565792900758322</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.2963782229283602</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.4678020148838795</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>-0.0452264693926312</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.8706046448976331</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>-0.09352882951066699</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.06128603667882748</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.0002535315041187758</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1145251377344681</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.1732872931401137</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.9649122807017544</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.237660847618366</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.1045693220900867</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.7670652811375739</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.3921442095204601</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>-0.09444023883315877</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.7298014104598676</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>-0.07741687217408433</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.1581520768513234</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.09154899325217558</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1771492010844213</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.2461249587924721</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.9395711500974658</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.3398215970939726</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.04345354862296746</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1.096795503018999</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-0.3398215970939727</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.7543016732344996</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.1411353747440025</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.403795878337594</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-0.1049631221034131</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.1397885555120524</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.07424152247084126</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1818140869661326</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.2520711548688638</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.9434697855750487</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.343396896459686</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.04863387549496068</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1.108335005804564</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>-0.3433968964596861</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.7358866404475835</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.1291567933740858</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1.369524514448298</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-0.1077622875732581</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.1273573073874552</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.06252517135729563</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1821400660530844</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2502692357919135</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9454191033138402</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3407563776045505</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.04480797187624819</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.099812565704477</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3408596999336523</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.7100769261764752</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1123681313006502</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.32149125162987</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1054534314823259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>-0.2242012270138071</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.1032426212645815</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.3336266559947872</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>-0.2242012270138072</v>
@@ -4065,7 +4626,7 @@
         <v>-0.2242012270138071</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.2953423679490121</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -4094,25 +4655,25 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.001819212861407848</v>
+        <v>0.002612223632950217</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0005781995242402083</v>
+        <v>-0.002301461276906336</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-0.1861905825872663</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.08506656480904382</v>
+        <v>0.08459265268256663</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2842705024901429</v>
+        <v>0.2827498998792176</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>-0.1861905825872663</v>
@@ -4127,13 +4688,13 @@
         <v>-0.1861905825872663</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2265534973925623</v>
+        <v>0.2319987974831492</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.04615586541688288</v>
+        <v>-0.04890102573125765</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7924066941852083</v>
+        <v>0.7855249454869999</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>-0.06639663516197625</v>
@@ -4156,19 +4717,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.0347527195054822</v>
+        <v>-0.03273688296640065</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.0324344062146561</v>
+        <v>-0.0374773260509732</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>-0.1977751279185385</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.102894524153197</v>
+        <v>0.1023794629725772</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.278828778962905</v>
+        <v>0.2772716108878875</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -4189,13 +4750,13 @@
         <v>-0.1977751279185385</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2030923163962011</v>
+        <v>0.2056048719871759</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.06440073604938645</v>
+        <v>-0.06927704843308924</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.710347502475649</v>
+        <v>0.6961577284525311</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>-0.04392132259347603</v>
@@ -4218,19 +4779,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.04249523517146048</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.04718785371645051</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.1541243129380868</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.07462520970126199</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2323499724942579</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4251,13 +4812,13 @@
         <v>-0.1541243129380868</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.1319686562387929</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.1261239620911172</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.4468327966462841</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>-0.04910852885624428</v>
@@ -4280,19 +4841,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.03832826771717424</v>
+        <v>-0.03459148845114535</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.0360185421127458</v>
+        <v>-0.03932284233176719</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-0.1938287231324922</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.09969672440806285</v>
+        <v>0.09920833586214862</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2832775140836015</v>
+        <v>0.2817572713835914</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4313,13 +4874,13 @@
         <v>-0.1938287231324922</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1928876156683936</v>
+        <v>0.1975228332372316</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.07233654476469098</v>
+        <v>-0.07551635546875812</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.6746549474635332</v>
+        <v>0.6687927458864688</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>-0.06809052344706434</v>
@@ -4342,19 +4903,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.02943793469695388</v>
+        <v>-0.02645937656591835</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.0271068564530339</v>
+        <v>-0.03123058497305986</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-0.2051728224903451</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1050257154567922</v>
+        <v>0.1044778434432681</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2954859375373192</v>
+        <v>0.293858064365045</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4375,13 +4936,13 @@
         <v>-0.2051728224903451</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2210982371589283</v>
+        <v>0.2248456658016778</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.05039821439516878</v>
+        <v>-0.05442321959942975</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.7733260585852043</v>
+        <v>0.7613051502332882</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>-0.07019594153968067</v>
@@ -4404,19 +4965,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.04333413134981978</v>
+        <v>-0.03851870301874494</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.04103642873724656</v>
+        <v>-0.04323081008140095</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-0.1856244724967976</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09995226162961648</v>
+        <v>0.09947831423738925</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2763396704990286</v>
+        <v>0.2749222742536829</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4437,13 +4998,13 @@
         <v>-0.1856244724967976</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1747232527765494</v>
+        <v>0.1806362845026359</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.08646228085337915</v>
+        <v>-0.08855271493049111</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.61112221494444</v>
+        <v>0.6116165647247094</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>-0.07027295871809192</v>
